--- a/base/pacotes/placon-arminio-tavares/preliminar-placon-arminio-tavares.xlsx
+++ b/base/pacotes/placon-arminio-tavares/preliminar-placon-arminio-tavares.xlsx
@@ -645,7 +645,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Gerado em 2026-04-14T07:43:56 | AC=4090 m² | UR=55 | padrão=medio | 5 projetos similares de referência</t>
+          <t>Gerado em 2026-04-14T08:53:55 | AC=4090 m² | UR=55 | padrão=medio | 5 projetos similares de referência</t>
         </is>
       </c>
     </row>
@@ -718,13 +718,13 @@
         </is>
       </c>
       <c r="C5" s="7" t="n">
-        <v>1570943.2464</v>
+        <v>919832.0123039999</v>
       </c>
       <c r="D5" s="8" t="n">
-        <v>384.12</v>
+        <v>224.9132</v>
       </c>
       <c r="E5" s="9" t="n">
-        <v>0.1226573850845401</v>
+        <v>0.07557941531354055</v>
       </c>
       <c r="F5" s="5" t="n">
         <v>1</v>
@@ -733,16 +733,16 @@
         <v>12602.92</v>
       </c>
       <c r="H5" s="9" t="n">
-        <v>0.008022517700038537</v>
+        <v>0.01370132788533</v>
       </c>
       <c r="I5" s="5" t="inlineStr">
         <is>
-          <t>calibrado (n=14)</t>
+          <t>calibrado (n=131)</t>
         </is>
       </c>
       <c r="J5" s="5" t="inlineStr">
         <is>
-          <t>306–553</t>
+          <t>61–942</t>
         </is>
       </c>
     </row>
@@ -756,13 +756,13 @@
         </is>
       </c>
       <c r="C6" s="7" t="n">
-        <v>444429.8724</v>
+        <v>87952.291404</v>
       </c>
       <c r="D6" s="8" t="n">
-        <v>108.67</v>
+        <v>21.5057</v>
       </c>
       <c r="E6" s="9" t="n">
-        <v>0.03470055721424808</v>
+        <v>0.007226735611375452</v>
       </c>
       <c r="F6" s="5" t="n">
         <v>2</v>
@@ -771,16 +771,16 @@
         <v>15300</v>
       </c>
       <c r="H6" s="9" t="n">
-        <v>0.03442612873292538</v>
+        <v>0.1739579464703312</v>
       </c>
       <c r="I6" s="5" t="inlineStr">
         <is>
-          <t>calibrado (n=14)</t>
+          <t>calibrado (n=58)</t>
         </is>
       </c>
       <c r="J6" s="5" t="inlineStr">
         <is>
-          <t>65–146</t>
+          <t>6–145</t>
         </is>
       </c>
     </row>
@@ -794,13 +794,13 @@
         </is>
       </c>
       <c r="C7" s="7" t="n">
-        <v>757088.9664</v>
+        <v>800201.567724</v>
       </c>
       <c r="D7" s="8" t="n">
-        <v>185.12</v>
+        <v>195.6617</v>
       </c>
       <c r="E7" s="9" t="n">
-        <v>0.05911260836938995</v>
+        <v>0.06574979541108916</v>
       </c>
       <c r="F7" s="5" t="n">
         <v>4</v>
@@ -809,16 +809,16 @@
         <v>117847.54</v>
       </c>
       <c r="H7" s="9" t="n">
-        <v>0.1556587735789779</v>
+        <v>0.1472723183174857</v>
       </c>
       <c r="I7" s="5" t="inlineStr">
         <is>
-          <t>calibrado (n=14)</t>
+          <t>calibrado (n=63)</t>
         </is>
       </c>
       <c r="J7" s="5" t="inlineStr">
         <is>
-          <t>81–240</t>
+          <t>82–318</t>
         </is>
       </c>
     </row>
@@ -832,13 +832,13 @@
         </is>
       </c>
       <c r="C8" s="7" t="n">
-        <v>2677212.5064</v>
+        <v>2687588.943984</v>
       </c>
       <c r="D8" s="8" t="n">
-        <v>654.62</v>
+        <v>657.1572</v>
       </c>
       <c r="E8" s="9" t="n">
-        <v>0.2090335765491035</v>
+        <v>0.2208298887974714</v>
       </c>
       <c r="F8" s="5" t="n">
         <v>19</v>
@@ -847,16 +847,16 @@
         <v>1779722.85</v>
       </c>
       <c r="H8" s="9" t="n">
-        <v>0.6647671209310022</v>
+        <v>0.6622005399984244</v>
       </c>
       <c r="I8" s="5" t="inlineStr">
         <is>
-          <t>calibrado (n=14)</t>
+          <t>calibrado (n=56)</t>
         </is>
       </c>
       <c r="J8" s="5" t="inlineStr">
         <is>
-          <t>359–762</t>
+          <t>405–793</t>
         </is>
       </c>
     </row>
@@ -870,13 +870,13 @@
         </is>
       </c>
       <c r="C9" s="7" t="n">
-        <v>524874.6648</v>
+        <v>621869.7360960001</v>
       </c>
       <c r="D9" s="8" t="n">
-        <v>128.34</v>
+        <v>152.0568</v>
       </c>
       <c r="E9" s="9" t="n">
-        <v>0.04098159117398177</v>
+        <v>0.05109688554717098</v>
       </c>
       <c r="F9" s="5" t="n">
         <v>9</v>
@@ -885,16 +885,16 @@
         <v>160281.93</v>
       </c>
       <c r="H9" s="9" t="n">
-        <v>0.3053718168337852</v>
+        <v>0.2577419686094143</v>
       </c>
       <c r="I9" s="5" t="inlineStr">
         <is>
-          <t>calibrado (n=14)</t>
+          <t>calibrado (n=130)</t>
         </is>
       </c>
       <c r="J9" s="5" t="inlineStr">
         <is>
-          <t>71–176</t>
+          <t>92–320</t>
         </is>
       </c>
     </row>
@@ -908,13 +908,13 @@
         </is>
       </c>
       <c r="C10" s="7" t="n">
-        <v>275033.67</v>
+        <v>250256.919324</v>
       </c>
       <c r="D10" s="8" t="n">
-        <v>67.25</v>
+        <v>61.1917</v>
       </c>
       <c r="E10" s="9" t="n">
-        <v>0.02147430268388869</v>
+        <v>0.02056274557492214</v>
       </c>
       <c r="F10" s="5" t="n">
         <v>15</v>
@@ -923,16 +923,16 @@
         <v>110491.47</v>
       </c>
       <c r="H10" s="9" t="n">
-        <v>0.4017379762994109</v>
+        <v>0.4415121479896029</v>
       </c>
       <c r="I10" s="5" t="inlineStr">
         <is>
-          <t>calibrado (n=11)</t>
+          <t>calibrado (n=61)</t>
         </is>
       </c>
       <c r="J10" s="5" t="inlineStr">
         <is>
-          <t>36–95</t>
+          <t>35–577</t>
         </is>
       </c>
     </row>
@@ -946,13 +946,13 @@
         </is>
       </c>
       <c r="C11" s="7" t="n">
-        <v>1215587.4756</v>
+        <v>1127373.851088</v>
       </c>
       <c r="D11" s="8" t="n">
-        <v>297.23</v>
+        <v>275.6604</v>
       </c>
       <c r="E11" s="9" t="n">
-        <v>0.09491162805549791</v>
+        <v>0.09263241044588184</v>
       </c>
       <c r="F11" s="5" t="n">
         <v>30</v>
@@ -961,16 +961,16 @@
         <v>61682.12</v>
       </c>
       <c r="H11" s="9" t="n">
-        <v>0.05074264192262627</v>
+        <v>0.05471310155053904</v>
       </c>
       <c r="I11" s="5" t="inlineStr">
         <is>
-          <t>calibrado (n=12)</t>
+          <t>calibrado (n=80)</t>
         </is>
       </c>
       <c r="J11" s="5" t="inlineStr">
         <is>
-          <t>42–371</t>
+          <t>28–447</t>
         </is>
       </c>
     </row>
@@ -984,13 +984,13 @@
         </is>
       </c>
       <c r="C12" s="7" t="n">
-        <v>714964.8503999999</v>
+        <v>667337.2216111812</v>
       </c>
       <c r="D12" s="8" t="n">
-        <v>174.82</v>
+        <v>163.1743057253751</v>
       </c>
       <c r="E12" s="9" t="n">
-        <v>0.0558236073635304</v>
+        <v>0.05483279158767367</v>
       </c>
       <c r="F12" s="5" t="n">
         <v>5</v>
@@ -999,16 +999,16 @@
         <v>13775.36</v>
       </c>
       <c r="H12" s="9" t="n">
-        <v>0.01926718494243896</v>
+        <v>0.0206422773283072</v>
       </c>
       <c r="I12" s="5" t="inlineStr">
         <is>
-          <t>calibrado (n=13)</t>
+          <t>calibrado (n=59)</t>
         </is>
       </c>
       <c r="J12" s="5" t="inlineStr">
         <is>
-          <t>99–243</t>
+          <t>96–255</t>
         </is>
       </c>
     </row>
@@ -1022,13 +1022,13 @@
         </is>
       </c>
       <c r="C13" s="7" t="n">
-        <v>134510.8908</v>
+        <v>160502.288316</v>
       </c>
       <c r="D13" s="8" t="n">
-        <v>32.89</v>
+        <v>39.2453</v>
       </c>
       <c r="E13" s="9" t="n">
-        <v>0.0105024507847301</v>
+        <v>0.01318791795147858</v>
       </c>
       <c r="F13" s="5" t="n">
         <v>20</v>
@@ -1037,16 +1037,16 @@
         <v>12842.66</v>
       </c>
       <c r="H13" s="9" t="n">
-        <v>0.09547672997791194</v>
+        <v>0.08001543239505174</v>
       </c>
       <c r="I13" s="5" t="inlineStr">
         <is>
-          <t>calibrado (n=4)</t>
+          <t>calibrado (n=18)</t>
         </is>
       </c>
       <c r="J13" s="5" t="inlineStr">
         <is>
-          <t>21–68</t>
+          <t>23–125</t>
         </is>
       </c>
     </row>
@@ -1060,13 +1060,13 @@
         </is>
       </c>
       <c r="C14" s="7" t="n">
-        <v>194302.5972</v>
+        <v>383622.2795519999</v>
       </c>
       <c r="D14" s="8" t="n">
-        <v>47.51</v>
+        <v>93.80159999999999</v>
       </c>
       <c r="E14" s="9" t="n">
-        <v>0.01517091629013459</v>
+        <v>0.03152091599548006</v>
       </c>
       <c r="F14" s="5" t="n">
         <v>3</v>
@@ -1075,16 +1075,16 @@
         <v>28578.95</v>
       </c>
       <c r="H14" s="9" t="n">
-        <v>0.1470847554887959</v>
+        <v>0.07449762832694426</v>
       </c>
       <c r="I14" s="5" t="inlineStr">
         <is>
-          <t>calibrado (n=4)</t>
+          <t>calibrado (n=61)</t>
         </is>
       </c>
       <c r="J14" s="5" t="inlineStr">
         <is>
-          <t>33–61</t>
+          <t>38–899</t>
         </is>
       </c>
     </row>
@@ -1098,13 +1098,13 @@
         </is>
       </c>
       <c r="C15" s="7" t="n">
-        <v>245792.172</v>
+        <v>257939.867316</v>
       </c>
       <c r="D15" s="8" t="n">
-        <v>60.1</v>
+        <v>63.0703</v>
       </c>
       <c r="E15" s="9" t="n">
-        <v>0.01919116120894736</v>
+        <v>0.02119402684079724</v>
       </c>
       <c r="F15" s="5" t="n">
         <v>1</v>
@@ -1113,16 +1113,16 @@
         <v>128482.47</v>
       </c>
       <c r="H15" s="9" t="n">
-        <v>0.5227280793954658</v>
+        <v>0.4981101655084485</v>
       </c>
       <c r="I15" s="5" t="inlineStr">
         <is>
-          <t>calibrado (n=11)</t>
+          <t>calibrado (n=35)</t>
         </is>
       </c>
       <c r="J15" s="5" t="inlineStr">
         <is>
-          <t>34–103</t>
+          <t>34–119</t>
         </is>
       </c>
     </row>
@@ -1136,13 +1136,13 @@
         </is>
       </c>
       <c r="C16" s="7" t="n">
-        <v>654641.4803999999</v>
+        <v>825622.4493</v>
       </c>
       <c r="D16" s="8" t="n">
-        <v>160.07</v>
+        <v>201.8775</v>
       </c>
       <c r="E16" s="9" t="n">
-        <v>0.05111363019494516</v>
+        <v>0.06783854133487623</v>
       </c>
       <c r="F16" s="5" t="n">
         <v>7</v>
@@ -1151,16 +1151,16 @@
         <v>316677.72</v>
       </c>
       <c r="H16" s="9" t="n">
-        <v>0.483742215367262</v>
+        <v>0.3835623901318256</v>
       </c>
       <c r="I16" s="5" t="inlineStr">
         <is>
-          <t>calibrado (n=10)</t>
+          <t>calibrado (n=42)</t>
         </is>
       </c>
       <c r="J16" s="5" t="inlineStr">
         <is>
-          <t>125–269</t>
+          <t>125–638</t>
         </is>
       </c>
     </row>
@@ -1174,13 +1174,13 @@
         </is>
       </c>
       <c r="C17" s="7" t="n">
-        <v>551089.77</v>
+        <v>511137.29532</v>
       </c>
       <c r="D17" s="8" t="n">
-        <v>134.75</v>
+        <v>124.981</v>
       </c>
       <c r="E17" s="9" t="n">
-        <v>0.04302843548927882</v>
+        <v>0.0419983838445303</v>
       </c>
       <c r="F17" s="5" t="n">
         <v>12</v>
@@ -1189,16 +1189,16 @@
         <v>282975.04</v>
       </c>
       <c r="H17" s="9" t="n">
-        <v>0.5134826581883383</v>
+        <v>0.5536184555322696</v>
       </c>
       <c r="I17" s="5" t="inlineStr">
         <is>
-          <t>calibrado (n=11)</t>
+          <t>calibrado (n=61)</t>
         </is>
       </c>
       <c r="J17" s="5" t="inlineStr">
         <is>
-          <t>104–168</t>
+          <t>60–193</t>
         </is>
       </c>
     </row>
@@ -1212,13 +1212,13 @@
         </is>
       </c>
       <c r="C18" s="7" t="n">
-        <v>1135797.0384</v>
+        <v>1260068.906208</v>
       </c>
       <c r="D18" s="8" t="n">
-        <v>277.72</v>
+        <v>308.1064</v>
       </c>
       <c r="E18" s="9" t="n">
-        <v>0.08868168537352515</v>
+        <v>0.1035355042138916</v>
       </c>
       <c r="F18" s="5" t="n">
         <v>5</v>
@@ -1227,16 +1227,16 @@
         <v>144197.49</v>
       </c>
       <c r="H18" s="9" t="n">
-        <v>0.126957092794617</v>
+        <v>0.114436194155399</v>
       </c>
       <c r="I18" s="5" t="inlineStr">
         <is>
-          <t>calibrado (n=14)</t>
+          <t>calibrado (n=56)</t>
         </is>
       </c>
       <c r="J18" s="5" t="inlineStr">
         <is>
-          <t>219–356</t>
+          <t>235–548</t>
         </is>
       </c>
     </row>
@@ -1250,13 +1250,13 @@
         </is>
       </c>
       <c r="C19" s="7" t="n">
-        <v>196551.9432</v>
+        <v>136252.293576</v>
       </c>
       <c r="D19" s="8" t="n">
-        <v>48.06</v>
+        <v>33.3158</v>
       </c>
       <c r="E19" s="9" t="n">
-        <v>0.01534654255743777</v>
+        <v>0.01119537974962276</v>
       </c>
       <c r="F19" s="5" t="n">
         <v>12</v>
@@ -1265,16 +1265,16 @@
         <v>37467.79</v>
       </c>
       <c r="H19" s="9" t="n">
-        <v>0.1906253857886051</v>
+        <v>0.2749883250890077</v>
       </c>
       <c r="I19" s="5" t="inlineStr">
         <is>
-          <t>calibrado (n=9)</t>
+          <t>calibrado (n=21)</t>
         </is>
       </c>
       <c r="J19" s="5" t="inlineStr">
         <is>
-          <t>23–234</t>
+          <t>23–518</t>
         </is>
       </c>
     </row>
@@ -1288,13 +1288,13 @@
         </is>
       </c>
       <c r="C20" s="7" t="n">
-        <v>577263.978</v>
+        <v>549960.189336</v>
       </c>
       <c r="D20" s="8" t="n">
-        <v>141.15</v>
+        <v>134.4738</v>
       </c>
       <c r="E20" s="9" t="n">
-        <v>0.04507208659971581</v>
+        <v>0.04518832678113152</v>
       </c>
       <c r="F20" s="5" t="n">
         <v>1</v>
@@ -1303,16 +1303,16 @@
         <v>45450.49</v>
       </c>
       <c r="H20" s="9" t="n">
-        <v>0.07873432559826207</v>
+        <v>0.08264323651294671</v>
       </c>
       <c r="I20" s="5" t="inlineStr">
         <is>
-          <t>calibrado (n=9)</t>
+          <t>calibrado (n=33)</t>
         </is>
       </c>
       <c r="J20" s="5" t="inlineStr">
         <is>
-          <t>70–253</t>
+          <t>68–253</t>
         </is>
       </c>
     </row>
@@ -1326,13 +1326,13 @@
         </is>
       </c>
       <c r="C21" s="7" t="n">
-        <v>745801.3392</v>
+        <v>714777.132252</v>
       </c>
       <c r="D21" s="8" t="n">
-        <v>182.36</v>
+        <v>174.7741</v>
       </c>
       <c r="E21" s="9" t="n">
-        <v>0.058231283828014</v>
+        <v>0.05873076497933545</v>
       </c>
       <c r="F21" s="5" t="n">
         <v>30</v>
@@ -1341,16 +1341,16 @@
         <v>258189.68</v>
       </c>
       <c r="H21" s="9" t="n">
-        <v>0.3461909578721765</v>
+        <v>0.3612170400395144</v>
       </c>
       <c r="I21" s="5" t="inlineStr">
         <is>
-          <t>calibrado (n=11)</t>
+          <t>calibrado (n=57)</t>
         </is>
       </c>
       <c r="J21" s="5" t="inlineStr">
         <is>
-          <t>81–274</t>
+          <t>70–365</t>
         </is>
       </c>
     </row>
@@ -1364,13 +1364,13 @@
         </is>
       </c>
       <c r="C22" s="7" t="n">
-        <v>191685.1764</v>
+        <v>208108.673976</v>
       </c>
       <c r="D22" s="8" t="n">
-        <v>46.87</v>
+        <v>50.8858</v>
       </c>
       <c r="E22" s="9" t="n">
-        <v>0.01496655117909089</v>
+        <v>0.017099570019731</v>
       </c>
       <c r="F22" s="5" t="n">
         <v>0</v>
@@ -1383,12 +1383,12 @@
       </c>
       <c r="I22" s="5" t="inlineStr">
         <is>
-          <t>calibrado (n=8)</t>
+          <t>calibrado (n=23)</t>
         </is>
       </c>
       <c r="J22" s="5" t="inlineStr">
         <is>
-          <t>34–58</t>
+          <t>39–95</t>
         </is>
       </c>
     </row>
@@ -1399,10 +1399,10 @@
         </is>
       </c>
       <c r="C23" s="11" t="n">
-        <v>12807571.638</v>
+        <v>12170403.91868718</v>
       </c>
       <c r="D23" s="12" t="n">
-        <v>3131.65</v>
+        <v>2975.852605725375</v>
       </c>
       <c r="E23" s="13" t="n">
         <v>1</v>
@@ -1411,7 +1411,7 @@
         <v>3526566.480000001</v>
       </c>
       <c r="H23" s="13" t="n">
-        <v>0.2753501272276078</v>
+        <v>0.2897657714207082</v>
       </c>
     </row>
     <row r="25">
@@ -1489,7 +1489,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Total calibrado V2 (mediana de 4 refs): R$ 134.511  |  R$/m²: 32.89</t>
+          <t>Total calibrado V2 (mediana de 18 refs): R$ 160.502  |  R$/m²: 39.25</t>
         </is>
       </c>
     </row>
@@ -2199,7 +2199,7 @@
         </is>
       </c>
       <c r="F27" s="27" t="n">
-        <v>0.09547671696781301</v>
+        <v>0.08001542149178041</v>
       </c>
     </row>
   </sheetData>
@@ -2242,7 +2242,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Total calibrado V2 (mediana de 4 refs): R$ 194.303  |  R$/m²: 47.51</t>
+          <t>Total calibrado V2 (mediana de 61 refs): R$ 383.622  |  R$/m²: 93.80</t>
         </is>
       </c>
     </row>
@@ -2408,7 +2408,7 @@
         </is>
       </c>
       <c r="F10" s="27" t="n">
-        <v>0.1470847614125459</v>
+        <v>0.07449763132729138</v>
       </c>
     </row>
   </sheetData>
@@ -2451,7 +2451,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Total calibrado V2 (mediana de 11 refs): R$ 245.792  |  R$/m²: 60.10</t>
+          <t>Total calibrado V2 (mediana de 35 refs): R$ 257.940  |  R$/m²: 63.07</t>
         </is>
       </c>
     </row>
@@ -2553,7 +2553,7 @@
         </is>
       </c>
       <c r="F8" s="27" t="n">
-        <v>0.5227280822637428</v>
+        <v>0.4981101682416437</v>
       </c>
     </row>
   </sheetData>
@@ -2596,7 +2596,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Total calibrado V2 (mediana de 10 refs): R$ 654.641  |  R$/m²: 160.07</t>
+          <t>Total calibrado V2 (mediana de 42 refs): R$ 825.622  |  R$/m²: 201.88</t>
         </is>
       </c>
     </row>
@@ -2890,7 +2890,7 @@
         </is>
       </c>
       <c r="F14" s="27" t="n">
-        <v>0.4837422108269907</v>
+        <v>0.3835623865318145</v>
       </c>
     </row>
   </sheetData>
@@ -2933,7 +2933,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Total calibrado V2 (mediana de 11 refs): R$ 551.090  |  R$/m²: 134.75</t>
+          <t>Total calibrado V2 (mediana de 61 refs): R$ 511.137  |  R$/m²: 124.98</t>
         </is>
       </c>
     </row>
@@ -3387,7 +3387,7 @@
         </is>
       </c>
       <c r="F19" s="27" t="n">
-        <v>0.5134826509608408</v>
+        <v>0.5536184477398428</v>
       </c>
     </row>
   </sheetData>
@@ -3430,7 +3430,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Total calibrado V2 (mediana de 14 refs): R$ 1.135.797  |  R$/m²: 277.72</t>
+          <t>Total calibrado V2 (mediana de 56 refs): R$ 1.260.069  |  R$/m²: 308.11</t>
         </is>
       </c>
     </row>
@@ -3660,7 +3660,7 @@
         </is>
       </c>
       <c r="F12" s="27" t="n">
-        <v>0.1269570894419054</v>
+        <v>0.1144361911333421</v>
       </c>
     </row>
   </sheetData>
@@ -3703,7 +3703,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Total calibrado V2 (mediana de 9 refs): R$ 196.552  |  R$/m²: 48.06</t>
+          <t>Total calibrado V2 (mediana de 21 refs): R$ 136.252  |  R$/m²: 33.32</t>
         </is>
       </c>
     </row>
@@ -4157,7 +4157,7 @@
         </is>
       </c>
       <c r="F19" s="27" t="n">
-        <v>0.1906253993015725</v>
+        <v>0.2749883445822576</v>
       </c>
     </row>
   </sheetData>
@@ -4200,7 +4200,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Total calibrado V2 (mediana de 9 refs): R$ 577.264  |  R$/m²: 141.15</t>
+          <t>Total calibrado V2 (mediana de 33 refs): R$ 549.960  |  R$/m²: 134.47</t>
         </is>
       </c>
     </row>
@@ -4302,7 +4302,7 @@
         </is>
       </c>
       <c r="F8" s="27" t="n">
-        <v>0.07873431793279156</v>
+        <v>0.08264322846690976</v>
       </c>
     </row>
   </sheetData>
@@ -4345,7 +4345,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Total calibrado V2 (mediana de 11 refs): R$ 745.801  |  R$/m²: 182.36</t>
+          <t>Total calibrado V2 (mediana de 57 refs): R$ 714.777  |  R$/m²: 174.77</t>
         </is>
       </c>
     </row>
@@ -5263,7 +5263,7 @@
         </is>
       </c>
       <c r="F37" s="27" t="n">
-        <v>0.346190955592749</v>
+        <v>0.3612170376611507</v>
       </c>
     </row>
   </sheetData>
@@ -5306,7 +5306,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Total calibrado V2 (mediana de 8 refs): R$ 191.685  |  R$/m²: 46.87</t>
+          <t>Total calibrado V2 (mediana de 23 refs): R$ 208.109  |  R$/m²: 50.89</t>
         </is>
       </c>
     </row>
@@ -5407,7 +5407,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Total calibrado V2 (mediana de 14 refs): R$ 1.570.943  |  R$/m²: 384.12</t>
+          <t>Total calibrado V2 (mediana de 131 refs): R$ 919.832  |  R$/m²: 224.91</t>
         </is>
       </c>
     </row>
@@ -5509,7 +5509,7 @@
         </is>
       </c>
       <c r="F8" s="27" t="n">
-        <v>0.008022515287475251</v>
+        <v>0.01370132376501243</v>
       </c>
     </row>
   </sheetData>
@@ -6121,7 +6121,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Total calibrado V2 (mediana de 14 refs): R$ 444.430  |  R$/m²: 108.67</t>
+          <t>Total calibrado V2 (mediana de 58 refs): R$ 87.952  |  R$/m²: 21.51</t>
         </is>
       </c>
     </row>
@@ -6255,7 +6255,7 @@
         </is>
       </c>
       <c r="F9" s="27" t="n">
-        <v>0.03442612337324966</v>
+        <v>0.1739579193874666</v>
       </c>
     </row>
   </sheetData>
@@ -6298,7 +6298,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Total calibrado V2 (mediana de 14 refs): R$ 757.089  |  R$/m²: 185.12</t>
+          <t>Total calibrado V2 (mediana de 63 refs): R$ 800.202  |  R$/m²: 195.66</t>
         </is>
       </c>
     </row>
@@ -6496,7 +6496,7 @@
         </is>
       </c>
       <c r="F11" s="27" t="n">
-        <v>0.1556587778056938</v>
+        <v>0.1472723223164781</v>
       </c>
     </row>
   </sheetData>
@@ -6539,7 +6539,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Total calibrado V2 (mediana de 14 refs): R$ 2.677.213  |  R$/m²: 654.62</t>
+          <t>Total calibrado V2 (mediana de 56 refs): R$ 2.687.589  |  R$/m²: 657.16</t>
         </is>
       </c>
     </row>
@@ -7217,7 +7217,7 @@
         </is>
       </c>
       <c r="F26" s="27" t="n">
-        <v>0.6647671220030125</v>
+        <v>0.6622005410662959</v>
       </c>
     </row>
   </sheetData>
@@ -7260,7 +7260,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Total calibrado V2 (mediana de 14 refs): R$ 524.875  |  R$/m²: 128.34</t>
+          <t>Total calibrado V2 (mediana de 130 refs): R$ 621.870  |  R$/m²: 152.06</t>
         </is>
       </c>
     </row>
@@ -7618,7 +7618,7 @@
         </is>
       </c>
       <c r="F16" s="27" t="n">
-        <v>0.3053718161936323</v>
+        <v>0.2577419680691082</v>
       </c>
     </row>
   </sheetData>
@@ -7661,7 +7661,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Total calibrado V2 (mediana de 11 refs): R$ 275.034  |  R$/m²: 67.25</t>
+          <t>Total calibrado V2 (mediana de 61 refs): R$ 250.257  |  R$/m²: 61.19</t>
         </is>
       </c>
     </row>
@@ -8211,7 +8211,7 @@
         </is>
       </c>
       <c r="F22" s="27" t="n">
-        <v>0.401737972056294</v>
+        <v>0.4415121433263951</v>
       </c>
     </row>
   </sheetData>
@@ -8254,7 +8254,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Total calibrado V2 (mediana de 12 refs): R$ 1.215.587  |  R$/m²: 297.23</t>
+          <t>Total calibrado V2 (mediana de 80 refs): R$ 1.127.374  |  R$/m²: 275.66</t>
         </is>
       </c>
     </row>
@@ -9284,7 +9284,7 @@
         </is>
       </c>
       <c r="F37" s="27" t="n">
-        <v>0.05074263929015425</v>
+        <v>0.05471309871208397</v>
       </c>
     </row>
   </sheetData>
@@ -9327,7 +9327,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Total calibrado V2 (mediana de 13 refs): R$ 714.965  |  R$/m²: 174.82</t>
+          <t>Total calibrado V2 (mediana de 59 refs): R$ 667.337  |  R$/m²: 163.17</t>
         </is>
       </c>
     </row>
@@ -9557,7 +9557,7 @@
         </is>
       </c>
       <c r="F12" s="27" t="n">
-        <v>0.01926717896172537</v>
+        <v>0.02064227092075212</v>
       </c>
     </row>
   </sheetData>
